--- a/public/templates/students-template.xlsx
+++ b/public/templates/students-template.xlsx
@@ -46,11 +46,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00374151"/>
       <sz val="10"/>
     </font>
@@ -58,6 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00374151"/>
       <sz val="10"/>
     </font>
     <font>
@@ -135,22 +136,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -516,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -525,12 +524,14 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -571,25 +572,35 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>campus_code</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>student_type</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>level</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>entry_year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>graduation_year</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>phone_number</t>
         </is>
@@ -606,11 +617,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -630,7 +641,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1. Fill in your student data on the 'Upload Data' sheet starting from row 2.</t>
+          <t>1. Fill in student data on the 'Upload Data' sheet starting from row 2.</t>
         </is>
       </c>
     </row>
@@ -644,213 +655,245 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>3. Save this file as CSV (comma separated) before uploading.</t>
+          <t>3. campus_code must match an existing campus code in the system (e.g. WIN, KSI, MMP, AMC).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   In Excel: File → Save As → CSV UTF-8 (Comma delimited) (*.csv)</t>
+          <t>4. programme_code must match an existing programme code (e.g. BSC_BED, BED_MATH).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>4. Go to Bulk Upload → Student Import and upload the CSV file.</t>
+          <t>5. Save as CSV: File → Save As → CSV UTF-8 (Comma delimited) (*.csv)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>5. A summary will show how many rows were imported and any errors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+          <t>6. Go to Bulk Upload → Student Import and upload the CSV file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>7. Duplicate index numbers are automatically skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>COLUMN REFERENCE</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>index_number</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Student index number (unique, required)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Student index number — must be unique e.g. WIN/2023/001 (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>first_name</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Student first name (required)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Student's first name (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>middle_name</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Student middle name (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Student's middle name — leave blank if none (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>last_name</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Student last name (required)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Student's last name / surname (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>date_of_birth</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Date in YYYY-MM-DD format e.g. 1998-05-20 (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Date of birth in YYYY-MM-DD format e.g. 2000-05-15 (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>MALE, FEMALE, or OTHER (optional)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>programme_code</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Programme code from the Programmes page (required)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Programme code from the Programmes page e.g. BSC_BED (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>campus_code</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Campus code e.g. WIN (Winneba), KSI (Kumasi), MMP (Mampong) (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>student_type</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>UNDERGRADUATE or POSTGRADUATE — defaults to UNDERGRADUATE if blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>100, 200, 300, 400 etc. (required)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Academic level: 100, 200, 300, 400 or 500 for postgraduate (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>entry_year</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>4-digit year e.g. 2022 (required)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>4-digit year of entry e.g. 2022 (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>graduation_year</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>4-digit year — leave blank if still active (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>4-digit graduation year — leave blank if student is still active (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Student email address (optional)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>phone_number</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Phone number (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>NOTE: Duplicate index numbers are automatically skipped. The programme_code must match an existing programme in the system.</t>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Student phone number (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>NOTE: Columns can be in any order as long as the header names match exactly.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
